--- a/tame_output/ON/bt/strategyON_20240309.xlsx
+++ b/tame_output/ON/bt/strategyON_20240309.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-137.6%</t>
+          <t>-137.8%</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-50.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-133.3%</t>
+          <t>-133.5%</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.4%</t>
         </is>
       </c>
     </row>
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>0.2396212804955432</v>
+        <v>0.238025504832135</v>
       </c>
       <c r="E1897" t="n">
-        <v>3.25909372545487</v>
+        <v>3.258455415189507</v>
       </c>
       <c r="F1897" t="n">
-        <v>0.9065374054799982</v>
+        <v>0.9048343718822711</v>
       </c>
       <c r="G1897" t="n">
-        <v>3.707524080858399</v>
+        <v>3.706502260699764</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240309.xlsx
+++ b/tame_output/ON/bt/strategyON_20240309.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>472.3%</t>
+          <t>469.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-137.8%</t>
+          <t>-166.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-50.4%</t>
+          <t>-61.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-133.5%</t>
+          <t>-143.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-81.2%</t>
         </is>
       </c>
     </row>
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>0.238025504832135</v>
+        <v>-0.04858613004046392</v>
       </c>
       <c r="E1897" t="n">
-        <v>3.258455415189507</v>
+        <v>3.143810761240467</v>
       </c>
       <c r="F1897" t="n">
-        <v>0.9048343718822711</v>
+        <v>0.8069060810619679</v>
       </c>
       <c r="G1897" t="n">
-        <v>3.706502260699764</v>
+        <v>3.647745286207581</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240309.xlsx
+++ b/tame_output/ON/bt/strategyON_20240309.xlsx
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.401222930316733</v>
+        <v>3.401222930316735</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>

--- a/tame_output/ON/bt/strategyON_20240309.xlsx
+++ b/tame_output/ON/bt/strategyON_20240309.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>-27.9%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>469.5%</t>
+          <t>469.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,52 +1456,52 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-81.2%</t>
+          <t>-163.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1897"/>
+  <dimension ref="A1:G1898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.401222930316735</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45192,6 +45192,29 @@
       </c>
       <c r="G1897" t="n">
         <v>3.647745286207581</v>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" s="2" t="n">
+        <v>45360</v>
+      </c>
+      <c r="B1898" t="n">
+        <v>3.40813904185096</v>
+      </c>
+      <c r="C1898" t="n">
+        <v>2.837508989757823</v>
+      </c>
+      <c r="D1898" t="n">
+        <v>-0.04858613004046392</v>
+      </c>
+      <c r="E1898" t="n">
+        <v>3.143810761240467</v>
+      </c>
+      <c r="F1898" t="n">
+        <v>0.8069060810619679</v>
+      </c>
+      <c r="G1898" t="n">
+        <v>2.830572786744191</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240309.xlsx
+++ b/tame_output/ON/bt/strategyON_20240309.xlsx
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.40813904185096</v>
+        <v>3.408139041850959</v>
       </c>
       <c r="C1898" t="n">
         <v>2.837508989757823</v>

--- a/tame_output/ON/bt/strategyON_20240309.xlsx
+++ b/tame_output/ON/bt/strategyON_20240309.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-27.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>469.6%</t>
+          <t>466.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-166.4%</t>
+          <t>-207.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-61.8%</t>
+          <t>-78.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-163.0%</t>
+          <t>-162.6%</t>
         </is>
       </c>
     </row>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-2.772947167657873</v>
+        <v>-3.184031467910765</v>
       </c>
       <c r="E1865" t="n">
-        <v>2.001090661038235</v>
+        <v>1.836656940937079</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.2366917757797393</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-2.769790466627669</v>
+        <v>-3.180874766880561</v>
       </c>
       <c r="E1866" t="n">
-        <v>2.000347392059195</v>
+        <v>1.835913671958038</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.2366917757797393</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-2.773803499040191</v>
+        <v>-3.184887799293084</v>
       </c>
       <c r="E1867" t="n">
-        <v>2.009000869762865</v>
+        <v>1.844567149661708</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.2366917757797393</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-2.787518363365303</v>
+        <v>-3.198602663618195</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.999614489178516</v>
+        <v>1.835180769077358</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.2366917757797393</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-2.793035283209269</v>
+        <v>-3.204119583462162</v>
       </c>
       <c r="E1869" t="n">
-        <v>1.99581264129593</v>
+        <v>1.831378921194773</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.2366917757797393</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-2.797848321674606</v>
+        <v>-3.208932621927498</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.997666401839004</v>
+        <v>1.833232681737846</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.2382384104825251</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-2.795731162950313</v>
+        <v>-3.206815463203205</v>
       </c>
       <c r="E1871" t="n">
-        <v>1.994486960794317</v>
+        <v>1.83005324069316</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.2382384104825251</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-2.795253816371823</v>
+        <v>-3.206338116624715</v>
       </c>
       <c r="E1872" t="n">
-        <v>1.994575798104129</v>
+        <v>1.830142078002972</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.2382384104825251</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-2.794229030064965</v>
+        <v>-3.205313330317858</v>
       </c>
       <c r="E1873" t="n">
-        <v>1.997557228598303</v>
+        <v>1.833123508497145</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.2372136241756675</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-2.812970410323884</v>
+        <v>-3.224054710576776</v>
       </c>
       <c r="E1874" t="n">
-        <v>1.995410979792785</v>
+        <v>1.830977259691628</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.2372136241756675</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-2.825939753108982</v>
+        <v>-3.237024053361875</v>
       </c>
       <c r="E1875" t="n">
-        <v>1.998139262635923</v>
+        <v>1.833705542534766</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.2501829669607661</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-2.819463606315423</v>
+        <v>-3.230547906568315</v>
       </c>
       <c r="E1876" t="n">
-        <v>2.003771471975116</v>
+        <v>1.839337751873959</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.2437068201672065</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-2.815772681359011</v>
+        <v>-3.226856981611904</v>
       </c>
       <c r="E1877" t="n">
-        <v>2.00524784195768</v>
+        <v>1.840814121856523</v>
       </c>
       <c r="F1877" t="n">
         <v>-0.2437068201672065</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-2.808557328487196</v>
+        <v>-3.219641628740088</v>
       </c>
       <c r="E1878" t="n">
-        <v>2.013647180225049</v>
+        <v>1.849213460123892</v>
       </c>
       <c r="F1878" t="n">
         <v>-0.1739285848768247</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-2.75752948240537</v>
+        <v>-3.168613782658262</v>
       </c>
       <c r="E1879" t="n">
-        <v>2.038540873142216</v>
+        <v>1.874107153041058</v>
       </c>
       <c r="F1879" t="n">
         <v>-0.0987192465697237</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-2.684059650737921</v>
+        <v>-3.095143950990814</v>
       </c>
       <c r="E1880" t="n">
-        <v>2.083300507302616</v>
+        <v>1.918866787201459</v>
       </c>
       <c r="F1880" t="n">
         <v>-0.02524941490227528</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-2.603687295273992</v>
+        <v>-3.014771595526884</v>
       </c>
       <c r="E1881" t="n">
-        <v>2.130004670235705</v>
+        <v>1.965570950134548</v>
       </c>
       <c r="F1881" t="n">
         <v>0.05512294056165434</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-2.570755425461141</v>
+        <v>-2.981839725714034</v>
       </c>
       <c r="E1882" t="n">
-        <v>2.135958253259249</v>
+        <v>1.971524533158092</v>
       </c>
       <c r="F1882" t="n">
         <v>0.05512294056165434</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-2.590920067010689</v>
+        <v>-3.002004367263581</v>
       </c>
       <c r="E1883" t="n">
-        <v>2.121220205865454</v>
+        <v>1.956786485764296</v>
       </c>
       <c r="F1883" t="n">
         <v>0.03495829901210701</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-2.532253136989155</v>
+        <v>-2.943337437242048</v>
       </c>
       <c r="E1884" t="n">
-        <v>2.145802767712623</v>
+        <v>1.981369047611466</v>
       </c>
       <c r="F1884" t="n">
         <v>0.1199177674422447</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-2.469183904682816</v>
+        <v>-2.880268204935708</v>
       </c>
       <c r="E1885" t="n">
-        <v>2.173724189264274</v>
+        <v>2.009290469163117</v>
       </c>
       <c r="F1885" t="n">
         <v>0.09140420476001021</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-2.417168390714003</v>
+        <v>-2.828252690966896</v>
       </c>
       <c r="E1886" t="n">
-        <v>2.1985207305382</v>
+        <v>2.034087010437043</v>
       </c>
       <c r="F1886" t="n">
         <v>0.09140420476001021</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-2.241598721793099</v>
+        <v>-2.652683022045992</v>
       </c>
       <c r="E1887" t="n">
-        <v>2.267273371207819</v>
+        <v>2.102839651106662</v>
       </c>
       <c r="F1887" t="n">
         <v>0.09140420476001021</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-2.044329316065101</v>
+        <v>-2.455413616317994</v>
       </c>
       <c r="E1888" t="n">
-        <v>2.361234543663891</v>
+        <v>2.196800823562734</v>
       </c>
       <c r="F1888" t="n">
         <v>0.2886736104880083</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-1.845177208828002</v>
+        <v>-2.256261509080895</v>
       </c>
       <c r="E1889" t="n">
-        <v>2.427844252912048</v>
+        <v>2.263410532810891</v>
       </c>
       <c r="F1889" t="n">
         <v>0.4539961364378217</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-1.619332056108591</v>
+        <v>-2.030416356361484</v>
       </c>
       <c r="E1890" t="n">
-        <v>2.527761387036021</v>
+        <v>2.363327666934864</v>
       </c>
       <c r="F1890" t="n">
         <v>0.4959228120249853</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-1.333057243785897</v>
+        <v>-1.744141544038789</v>
       </c>
       <c r="E1891" t="n">
-        <v>2.643410456521158</v>
+        <v>2.47897673642</v>
       </c>
       <c r="F1891" t="n">
         <v>0.4959228120249853</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-1.106261416712563</v>
+        <v>-1.517345716965455</v>
       </c>
       <c r="E1892" t="n">
-        <v>2.736762561512599</v>
+        <v>2.572328841411442</v>
       </c>
       <c r="F1892" t="n">
         <v>0.5640367566465299</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-0.8223526857838137</v>
+        <v>-1.233436986036706</v>
       </c>
       <c r="E1893" t="n">
-        <v>2.856059758122735</v>
+        <v>2.691626038021578</v>
       </c>
       <c r="F1893" t="n">
         <v>0.5640367566465299</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-0.5753654355908616</v>
+        <v>-0.9864497358437544</v>
       </c>
       <c r="E1894" t="n">
-        <v>2.94511739580605</v>
+        <v>2.780683675704894</v>
       </c>
       <c r="F1894" t="n">
         <v>0.8110240068394819</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-0.3115285683867925</v>
+        <v>-0.7226128686396853</v>
       </c>
       <c r="E1895" t="n">
-        <v>3.04076866137477</v>
+        <v>2.876334941273613</v>
       </c>
       <c r="F1895" t="n">
         <v>0.8110240068394819</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-0.04428676751839555</v>
+        <v>-0.4553710677712883</v>
       </c>
       <c r="E1896" t="n">
-        <v>3.145830821222756</v>
+        <v>2.981397101121599</v>
       </c>
       <c r="F1896" t="n">
         <v>0.8110240068394819</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-0.04858613004046392</v>
+        <v>-0.4596704302933567</v>
       </c>
       <c r="E1897" t="n">
-        <v>3.143810761240467</v>
+        <v>2.97937704113931</v>
       </c>
       <c r="F1897" t="n">
         <v>0.8069060810619679</v>
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.408139041850959</v>
+        <v>3.409981178823549</v>
       </c>
       <c r="C1898" t="n">
-        <v>2.837508989757823</v>
+        <v>2.841192864921219</v>
       </c>
       <c r="D1898" t="n">
-        <v>-0.04858613004046392</v>
+        <v>-0.4596704302933567</v>
       </c>
       <c r="E1898" t="n">
-        <v>3.143810761240467</v>
+        <v>2.97937704113931</v>
       </c>
       <c r="F1898" t="n">
         <v>0.8069060810619679</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.830572786744191</v>
+        <v>2.834256661907587</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240309.xlsx
+++ b/tame_output/ON/bt/strategyON_20240309.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>466.7%</t>
+          <t>468.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-207.5%</t>
+          <t>-179.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-67.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-143.3%</t>
+          <t>-134.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-3.184031467910765</v>
+        <v>-3.181115059544125</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.836656940937079</v>
+        <v>1.837823504283735</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.2366917757797393</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-3.180874766880561</v>
+        <v>-3.177958358513921</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.835913671958038</v>
+        <v>1.837080235304694</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.2366917757797393</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-3.184887799293084</v>
+        <v>-3.181971390926444</v>
       </c>
       <c r="E1867" t="n">
-        <v>1.844567149661708</v>
+        <v>1.845733713008364</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.2366917757797393</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-3.198602663618195</v>
+        <v>-3.195686255251555</v>
       </c>
       <c r="E1868" t="n">
-        <v>1.835180769077358</v>
+        <v>1.836347332424014</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.2366917757797393</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-3.204119583462162</v>
+        <v>-3.201203175095522</v>
       </c>
       <c r="E1869" t="n">
-        <v>1.831378921194773</v>
+        <v>1.832545484541429</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.2366917757797393</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-3.208932621927498</v>
+        <v>-3.206016213560858</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.833232681737846</v>
+        <v>1.834399245084502</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.2382384104825251</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-3.206815463203205</v>
+        <v>-3.203899054836565</v>
       </c>
       <c r="E1871" t="n">
-        <v>1.83005324069316</v>
+        <v>1.831219804039816</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.2382384104825251</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-3.206338116624715</v>
+        <v>-3.203421708258075</v>
       </c>
       <c r="E1872" t="n">
-        <v>1.830142078002972</v>
+        <v>1.831308641349628</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.2382384104825251</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-3.205313330317858</v>
+        <v>-3.202396921951218</v>
       </c>
       <c r="E1873" t="n">
-        <v>1.833123508497145</v>
+        <v>1.834290071843801</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.2372136241756675</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-3.224054710576776</v>
+        <v>-3.221138302210136</v>
       </c>
       <c r="E1874" t="n">
-        <v>1.830977259691628</v>
+        <v>1.832143823038284</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.2372136241756675</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-3.237024053361875</v>
+        <v>-3.234107644995235</v>
       </c>
       <c r="E1875" t="n">
-        <v>1.833705542534766</v>
+        <v>1.834872105881422</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.2501829669607661</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-3.230547906568315</v>
+        <v>-3.227631498201675</v>
       </c>
       <c r="E1876" t="n">
-        <v>1.839337751873959</v>
+        <v>1.840504315220615</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.2437068201672065</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-3.226856981611904</v>
+        <v>-3.223940573245264</v>
       </c>
       <c r="E1877" t="n">
-        <v>1.840814121856523</v>
+        <v>1.841980685203179</v>
       </c>
       <c r="F1877" t="n">
         <v>-0.2437068201672065</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-3.219641628740088</v>
+        <v>-3.216725220373448</v>
       </c>
       <c r="E1878" t="n">
-        <v>1.849213460123892</v>
+        <v>1.850380023470548</v>
       </c>
       <c r="F1878" t="n">
         <v>-0.1739285848768247</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-3.168613782658262</v>
+        <v>-3.165697374291622</v>
       </c>
       <c r="E1879" t="n">
-        <v>1.874107153041058</v>
+        <v>1.875273716387714</v>
       </c>
       <c r="F1879" t="n">
         <v>-0.0987192465697237</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-3.095143950990814</v>
+        <v>-3.092227542624174</v>
       </c>
       <c r="E1880" t="n">
-        <v>1.918866787201459</v>
+        <v>1.920033350548115</v>
       </c>
       <c r="F1880" t="n">
         <v>-0.02524941490227528</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-3.014771595526884</v>
+        <v>-3.011855187160244</v>
       </c>
       <c r="E1881" t="n">
-        <v>1.965570950134548</v>
+        <v>1.966737513481204</v>
       </c>
       <c r="F1881" t="n">
         <v>0.05512294056165434</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-2.981839725714034</v>
+        <v>-2.978923317347394</v>
       </c>
       <c r="E1882" t="n">
-        <v>1.971524533158092</v>
+        <v>1.972691096504748</v>
       </c>
       <c r="F1882" t="n">
         <v>0.05512294056165434</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-3.002004367263581</v>
+        <v>-2.999087958896941</v>
       </c>
       <c r="E1883" t="n">
-        <v>1.956786485764296</v>
+        <v>1.957953049110952</v>
       </c>
       <c r="F1883" t="n">
         <v>0.03495829901210701</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-2.943337437242048</v>
+        <v>-2.940421028875408</v>
       </c>
       <c r="E1884" t="n">
-        <v>1.981369047611466</v>
+        <v>1.982535610958122</v>
       </c>
       <c r="F1884" t="n">
         <v>0.1199177674422447</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-2.880268204935708</v>
+        <v>-2.877351796569068</v>
       </c>
       <c r="E1885" t="n">
-        <v>2.009290469163117</v>
+        <v>2.010457032509773</v>
       </c>
       <c r="F1885" t="n">
         <v>0.09140420476001021</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-2.828252690966896</v>
+        <v>-2.825336282600256</v>
       </c>
       <c r="E1886" t="n">
-        <v>2.034087010437043</v>
+        <v>2.035253573783699</v>
       </c>
       <c r="F1886" t="n">
         <v>0.09140420476001021</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-2.652683022045992</v>
+        <v>-2.649766613679352</v>
       </c>
       <c r="E1887" t="n">
-        <v>2.102839651106662</v>
+        <v>2.104006214453318</v>
       </c>
       <c r="F1887" t="n">
         <v>0.09140420476001021</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-2.455413616317994</v>
+        <v>-2.452497207951354</v>
       </c>
       <c r="E1888" t="n">
-        <v>2.196800823562734</v>
+        <v>2.19796738690939</v>
       </c>
       <c r="F1888" t="n">
         <v>0.2886736104880083</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-2.256261509080895</v>
+        <v>-2.253345100714255</v>
       </c>
       <c r="E1889" t="n">
-        <v>2.263410532810891</v>
+        <v>2.264577096157547</v>
       </c>
       <c r="F1889" t="n">
         <v>0.4539961364378217</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-2.030416356361484</v>
+        <v>-2.027499947994844</v>
       </c>
       <c r="E1890" t="n">
-        <v>2.363327666934864</v>
+        <v>2.36449423028152</v>
       </c>
       <c r="F1890" t="n">
         <v>0.4959228120249853</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-1.744141544038789</v>
+        <v>-1.741225135672149</v>
       </c>
       <c r="E1891" t="n">
-        <v>2.47897673642</v>
+        <v>2.480143299766656</v>
       </c>
       <c r="F1891" t="n">
         <v>0.4959228120249853</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-1.517345716965455</v>
+        <v>-1.514429308598815</v>
       </c>
       <c r="E1892" t="n">
-        <v>2.572328841411442</v>
+        <v>2.573495404758098</v>
       </c>
       <c r="F1892" t="n">
         <v>0.5640367566465299</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-1.233436986036706</v>
+        <v>-1.230520577670067</v>
       </c>
       <c r="E1893" t="n">
-        <v>2.691626038021578</v>
+        <v>2.692792601368234</v>
       </c>
       <c r="F1893" t="n">
         <v>0.5640367566465299</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-0.9864497358437544</v>
+        <v>-0.9835333274771144</v>
       </c>
       <c r="E1894" t="n">
-        <v>2.780683675704894</v>
+        <v>2.78185023905155</v>
       </c>
       <c r="F1894" t="n">
         <v>0.8110240068394819</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-0.7226128686396853</v>
+        <v>-0.7196964602730453</v>
       </c>
       <c r="E1895" t="n">
-        <v>2.876334941273613</v>
+        <v>2.877501504620269</v>
       </c>
       <c r="F1895" t="n">
         <v>0.8110240068394819</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-0.4553710677712883</v>
+        <v>-0.4524546594046484</v>
       </c>
       <c r="E1896" t="n">
-        <v>2.981397101121599</v>
+        <v>2.982563664468254</v>
       </c>
       <c r="F1896" t="n">
         <v>0.8110240068394819</v>
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-0.4596704302933567</v>
+        <v>-0.1766454960041642</v>
       </c>
       <c r="E1897" t="n">
-        <v>2.97937704113931</v>
+        <v>3.092587014854987</v>
       </c>
       <c r="F1897" t="n">
-        <v>0.8069060810619679</v>
+        <v>0.9000433151182154</v>
       </c>
       <c r="G1897" t="n">
-        <v>3.647745286207581</v>
+        <v>3.70362762664133</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,13 +45205,13 @@
         <v>2.841192864921219</v>
       </c>
       <c r="D1898" t="n">
-        <v>-0.4596704302933567</v>
+        <v>-0.1766454960041642</v>
       </c>
       <c r="E1898" t="n">
-        <v>2.97937704113931</v>
+        <v>3.092587014854987</v>
       </c>
       <c r="F1898" t="n">
-        <v>0.8069060810619679</v>
+        <v>0.9000433151182154</v>
       </c>
       <c r="G1898" t="n">
         <v>2.834256661907587</v>

--- a/tame_output/ON/bt/strategyON_20240309.xlsx
+++ b/tame_output/ON/bt/strategyON_20240309.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>468.7%</t>
+          <t>470.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-179.2%</t>
+          <t>-151.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-67.0%</t>
+          <t>-55.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,22 +1318,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-134.0%</t>
+          <t>-106.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,52 +1456,52 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-162.6%</t>
+          <t>-58.9%</t>
         </is>
       </c>
     </row>
@@ -45202,19 +45202,19 @@
         <v>3.409981178823549</v>
       </c>
       <c r="C1898" t="n">
-        <v>2.841192864921219</v>
+        <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-0.1766454960041642</v>
+        <v>0.1021138059477594</v>
       </c>
       <c r="E1898" t="n">
-        <v>3.092587014854987</v>
+        <v>3.20475924178125</v>
       </c>
       <c r="F1898" t="n">
-        <v>0.9000433151182154</v>
+        <v>1.178802617070139</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.834256661907587</v>
+        <v>3.871551713957978</v>
       </c>
     </row>
   </sheetData>
